--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_47.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6191263.684398304</v>
+        <v>6231200.863173384</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645785</v>
+        <v>6767152.318645782</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645785</v>
+        <v>6767152.318645782</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517487</v>
+        <v>2916902.906517483</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517487</v>
+        <v>2916902.906517483</v>
       </c>
     </row>
     <row r="11">
@@ -657,10 +657,10 @@
         <v>481.9993129555745</v>
       </c>
       <c r="C2" t="n">
-        <v>449.4745782429939</v>
+        <v>142.0842111174291</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
@@ -669,7 +669,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H2" t="n">
         <v>8.009658703527407</v>
@@ -678,7 +678,7 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>797.8013999999999</v>
+        <v>634.7678887921559</v>
       </c>
       <c r="K2" t="n">
         <v>97.12488247690055</v>
@@ -690,25 +690,25 @@
         <v>297.9910820919849</v>
       </c>
       <c r="N2" t="n">
+        <v>194.5855355810472</v>
+      </c>
+      <c r="O2" t="n">
         <v>814</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
-        <v>418.7212354311146</v>
+        <v>814</v>
       </c>
       <c r="Q2" t="n">
-        <v>797.8013999999999</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>187.4578006767583</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>297.9271412701616</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>466.5639999646113</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>57.93598414360956</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -842,10 +842,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617060965</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>297.3920501269246</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
@@ -909,19 +909,19 @@
         <v>403.7573722870162</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>814</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>224.1356998500677</v>
       </c>
       <c r="M5" t="n">
         <v>297.9910820919849</v>
@@ -930,10 +930,10 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P5" t="n">
-        <v>700.3237126680343</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>797.8013999999999</v>
@@ -942,7 +942,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>494.8481678023229</v>
+        <v>187.4578006767583</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -957,10 +957,10 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>203.9270655572417</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>175.4172848236332</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>57.72562438342279</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>466.5639999646113</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>297.3920501269255</v>
+        <v>297.3920501269214</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
@@ -1146,31 +1146,31 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>232.0824533610411</v>
+        <v>313.1545016101269</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
-        <v>814</v>
+        <v>297.9910820919849</v>
       </c>
       <c r="N8" t="n">
         <v>194.5855355810472</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>814</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>370.9706110579117</v>
@@ -1179,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>438.3363995050528</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1191,13 +1191,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>581.861707683677</v>
       </c>
       <c r="X8" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1213,16 +1213,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>131.9860885083954</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>167.1158402638074</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>114.9691617061037</v>
+        <v>114.9691617061039</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1368,16 +1368,16 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>15.15015635880158</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>208.5589096648669</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1526,19 +1526,19 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.572420793687957</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>3.77112610161862</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>18.28794854357571</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1608,13 +1608,13 @@
         <v>198.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>73.02920901914925</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>67.57968198731129</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>34.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1802,16 +1802,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>53.74128073011011</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>18.44220111900162</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>124.7573722870162</v>
+        <v>124.3267636724302</v>
       </c>
       <c r="H17" t="n">
         <v>129.0096587035274</v>
@@ -1893,7 +1893,7 @@
         <v>215.8481678023229</v>
       </c>
       <c r="T17" t="n">
-        <v>307.2449731139783</v>
+        <v>307.6755817285639</v>
       </c>
       <c r="U17" t="n">
         <v>370.2212965486107</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>424.7953317029608</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2085,13 +2085,13 @@
         <v>131.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>125.3632896068686</v>
+        <v>124.9326809922826</v>
       </c>
       <c r="F20" t="n">
         <v>125.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>124.3267636724302</v>
+        <v>124.7573722870162</v>
       </c>
       <c r="H20" t="n">
         <v>129.0096587035274</v>
@@ -2234,16 +2234,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.845755736583793</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2273,19 +2273,19 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>231.0944959041921</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>124.7573722870162</v>
+        <v>124.3267636724302</v>
       </c>
       <c r="H23" t="n">
         <v>129.0096587035274</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>215.4175591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2471,16 +2471,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2498,28 +2498,28 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>73.25953106976573</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2553,22 +2553,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>189.411675845388</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>54.80418743472489</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,10 +2601,10 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>424.2212965486107</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="R28" t="n">
-        <v>184.7308004571833</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>221.9364105579686</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>224.4745782429939</v>
+        <v>189.411675845388</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>18.28794854357566</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -3027,7 +3027,7 @@
         <v>190.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>158.4745782429939</v>
+        <v>166.9311696284081</v>
       </c>
       <c r="D32" t="n">
         <v>119.3391557398498</v>
@@ -3042,7 +3042,7 @@
         <v>112.7573722870162</v>
       </c>
       <c r="H32" t="n">
-        <v>125.4662500889416</v>
+        <v>117.0096587035274</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3051,7 +3051,7 @@
         <v>377.7382696589756</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320763738</v>
+        <v>10.23281455344341</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
@@ -3063,13 +3063,13 @@
         <v>153.5855355810893</v>
       </c>
       <c r="O32" t="n">
-        <v>397.7077537618813</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>686.9361823428895</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579538</v>
+        <v>757.6173000000409</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3221,16 +3221,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>70.05053078766994</v>
+        <v>156.2070946898295</v>
       </c>
       <c r="Q34" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3279,28 +3279,28 @@
         <v>112.7573722870162</v>
       </c>
       <c r="H35" t="n">
-        <v>117.0096587035274</v>
+        <v>125.4662500889416</v>
       </c>
       <c r="I35" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>757.6173000000483</v>
+        <v>377.7382696589829</v>
       </c>
       <c r="K35" t="n">
-        <v>712.6384842277181</v>
+        <v>773</v>
       </c>
       <c r="L35" t="n">
-        <v>185.8837068501973</v>
+        <v>727.1079320760799</v>
       </c>
       <c r="M35" t="n">
         <v>256.991082092034</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000493</v>
+        <v>153.5855355810966</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>397.7077537619013</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3455,22 +3455,22 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>194.5984637871033</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.3312422387043</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3519,16 +3519,16 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I38" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>757.6173000000554</v>
+        <v>377.7382696589902</v>
       </c>
       <c r="K38" t="n">
-        <v>10.23281455287789</v>
+        <v>351.8156858383957</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M38" t="n">
         <v>256.9910820920413</v>
@@ -3537,7 +3537,7 @@
         <v>153.5855355811038</v>
       </c>
       <c r="O38" t="n">
-        <v>734.7038409438936</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>773.0000000000566</v>
@@ -3546,7 +3546,7 @@
         <v>329.9706110579683</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3695,7 +3695,7 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>298.1276103623819</v>
+        <v>298.1276103624359</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>81.41167584538807</v>
+        <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>281.8481678023229</v>
+        <v>57.53639857163994</v>
       </c>
       <c r="T41" t="n">
         <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>436.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>416.8510241668239</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>334.2737972923793</v>
+        <v>196.8073545500588</v>
       </c>
       <c r="S42" t="n">
         <v>253.5639999646113</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>81.90670016750805</v>
+        <v>219.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>217.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>216.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>116.5904325512139</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>219.1384424760049</v>
       </c>
       <c r="T44" t="n">
         <v>399.6755817285639</v>
@@ -4041,7 +4041,7 @@
         <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>324.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4060,16 +4060,16 @@
         <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>138.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>30.12638589134853</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>360.2737972923793</v>
+        <v>62.48758491141504</v>
       </c>
       <c r="S45" t="n">
-        <v>255.3880753020965</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4190,10 +4190,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>702.4077201726793</v>
+        <v>1199.993207924634</v>
       </c>
       <c r="C2" t="n">
-        <v>248.3929946747056</v>
+        <v>1056.473802755514</v>
       </c>
       <c r="D2" t="n">
-        <v>237.9494030182917</v>
+        <v>641.9898070586958</v>
       </c>
       <c r="E2" t="n">
-        <v>233.5420397790304</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F2" t="n">
-        <v>228.6030208820488</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G2" t="n">
         <v>224.8076953396081</v>
@@ -4321,25 +4321,25 @@
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>65.12</v>
+        <v>229.8003143513576</v>
       </c>
       <c r="K2" t="n">
-        <v>772.8740581041409</v>
+        <v>937.5543724554984</v>
       </c>
       <c r="L2" t="n">
-        <v>1578.734058104141</v>
+        <v>1743.414372455498</v>
       </c>
       <c r="M2" t="n">
-        <v>2083.592965081934</v>
+        <v>2248.273279433291</v>
       </c>
       <c r="N2" t="n">
-        <v>2067.230742859711</v>
+        <v>2857.58223339183</v>
       </c>
       <c r="O2" t="n">
-        <v>2873.090742859712</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P2" t="n">
-        <v>3256</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q2" t="n">
         <v>3256</v>
@@ -4348,25 +4348,25 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2813.235960095906</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T2" t="n">
-        <v>2220.634362390286</v>
+        <v>2718.219850142241</v>
       </c>
       <c r="U2" t="n">
-        <v>1968.895679007851</v>
+        <v>2466.481166759806</v>
       </c>
       <c r="V2" t="n">
-        <v>1736.722927324191</v>
+        <v>2234.308415076146</v>
       </c>
       <c r="W2" t="n">
-        <v>1495.941638454547</v>
+        <v>1993.527126206502</v>
       </c>
       <c r="X2" t="n">
-        <v>1301.717564251852</v>
+        <v>1799.303052003807</v>
       </c>
       <c r="Y2" t="n">
-        <v>1189.275713057098</v>
+        <v>1686.861200809053</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C3" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="D3" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="E3" t="n">
-        <v>65.12</v>
+        <v>585.3760880419295</v>
       </c>
       <c r="F3" t="n">
-        <v>65.12</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>65.12</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>65.12</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="I3" t="n">
         <v>65.12</v>
@@ -4427,25 +4427,25 @@
         <v>1071.791008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>600.5142413210704</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>191.0619532225715</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>132.5407571179154</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V3" t="n">
-        <v>117.8835175305213</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W3" t="n">
-        <v>85.18337317715914</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X3" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y3" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="4">
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>530.9179093594554</v>
+        <v>576.073521926911</v>
       </c>
       <c r="C4" t="n">
-        <v>530.9179093594554</v>
+        <v>576.073521926911</v>
       </c>
       <c r="D4" t="n">
-        <v>530.9179093594554</v>
+        <v>576.073521926911</v>
       </c>
       <c r="E4" t="n">
-        <v>530.9179093594554</v>
+        <v>576.073521926911</v>
       </c>
       <c r="F4" t="n">
-        <v>530.9179093594554</v>
+        <v>700.4344945188465</v>
       </c>
       <c r="G4" t="n">
-        <v>684.3244752463406</v>
+        <v>853.8410604057317</v>
       </c>
       <c r="H4" t="n">
-        <v>853.8410604057382</v>
+        <v>853.8410604057317</v>
       </c>
       <c r="I4" t="n">
-        <v>1074.973939341821</v>
+        <v>1074.973939341815</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994272</v>
+        <v>1436.057679994266</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931134</v>
       </c>
       <c r="L4" t="n">
-        <v>1522.636630943485</v>
+        <v>1546.422113931134</v>
       </c>
       <c r="M4" t="n">
-        <v>1400.786518415657</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1227.87230096951</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O4" t="n">
-        <v>984.99799381899</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P4" t="n">
-        <v>694.6465823762856</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>365.5160102292168</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
@@ -4509,22 +4509,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>102.3702550941731</v>
+        <v>290.445934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>102.3702550941731</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="V4" t="n">
-        <v>135.8603527544536</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="W4" t="n">
-        <v>307.751271014131</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="X4" t="n">
-        <v>307.751271014131</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="Y4" t="n">
-        <v>419.1605716931633</v>
+        <v>536.9971268912645</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>702.4077201726793</v>
+        <v>1510.488528253487</v>
       </c>
       <c r="C5" t="n">
-        <v>652.4333987151097</v>
+        <v>1460.514206795918</v>
       </c>
       <c r="D5" t="n">
-        <v>641.9898070586958</v>
+        <v>1450.070615139504</v>
       </c>
       <c r="E5" t="n">
-        <v>637.5824438194345</v>
+        <v>1041.622847859838</v>
       </c>
       <c r="F5" t="n">
-        <v>632.6434249224528</v>
+        <v>1036.683828962857</v>
       </c>
       <c r="G5" t="n">
-        <v>224.8076953396081</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H5" t="n">
         <v>216.7171309926107</v>
@@ -4558,22 +4558,22 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K5" t="n">
-        <v>431.6498286273397</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L5" t="n">
-        <v>1237.50982862734</v>
+        <v>1352.334361285891</v>
       </c>
       <c r="M5" t="n">
-        <v>1742.368735605133</v>
+        <v>1857.193268263684</v>
       </c>
       <c r="N5" t="n">
-        <v>2351.677689563671</v>
+        <v>2466.502222222222</v>
       </c>
       <c r="O5" t="n">
-        <v>3157.537689563671</v>
+        <v>2450.14</v>
       </c>
       <c r="P5" t="n">
         <v>3256</v>
@@ -4585,25 +4585,25 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2502.740639767053</v>
+        <v>2813.235960095906</v>
       </c>
       <c r="T5" t="n">
-        <v>2314.179446101837</v>
+        <v>2624.67476643069</v>
       </c>
       <c r="U5" t="n">
-        <v>2062.440762719402</v>
+        <v>2372.936083048255</v>
       </c>
       <c r="V5" t="n">
-        <v>1830.268011035741</v>
+        <v>2140.763331364595</v>
       </c>
       <c r="W5" t="n">
-        <v>1589.486722166097</v>
+        <v>1899.982042494951</v>
       </c>
       <c r="X5" t="n">
-        <v>991.2222439229987</v>
+        <v>1705.757968292256</v>
       </c>
       <c r="Y5" t="n">
-        <v>785.2353090166939</v>
+        <v>1593.316117097502</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>65.12</v>
+        <v>754.3203429896864</v>
       </c>
       <c r="D6" t="n">
-        <v>65.12</v>
+        <v>754.3203429896864</v>
       </c>
       <c r="E6" t="n">
-        <v>65.12</v>
+        <v>408.1869114524009</v>
       </c>
       <c r="F6" t="n">
         <v>65.12</v>
@@ -4658,31 +4658,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1162.243708870129</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>609.4418934232809</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>138.1651257822594</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>132.7532417241646</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>132.5407571179154</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>117.8835175305213</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>85.18337317715914</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>905.4573541824243</v>
+        <v>65.12</v>
       </c>
       <c r="C7" t="n">
-        <v>905.4573541824243</v>
+        <v>175.4088884311033</v>
       </c>
       <c r="D7" t="n">
-        <v>905.4573541824243</v>
+        <v>288.7280325561034</v>
       </c>
       <c r="E7" t="n">
-        <v>905.4573541824243</v>
+        <v>406.5569367675164</v>
       </c>
       <c r="F7" t="n">
-        <v>905.4573541824243</v>
+        <v>530.9179093594519</v>
       </c>
       <c r="G7" t="n">
-        <v>905.4573541824243</v>
+        <v>684.3244752463371</v>
       </c>
       <c r="H7" t="n">
-        <v>1074.973939341822</v>
+        <v>853.8410604057347</v>
       </c>
       <c r="I7" t="n">
-        <v>1074.973939341822</v>
+        <v>1074.973939341818</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994273</v>
+        <v>1436.057679994269</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931142</v>
+        <v>1546.422113931137</v>
       </c>
       <c r="L7" t="n">
-        <v>1522.636630943486</v>
+        <v>1522.636630943482</v>
       </c>
       <c r="M7" t="n">
-        <v>1400.786518415658</v>
+        <v>1400.786518415654</v>
       </c>
       <c r="N7" t="n">
-        <v>1227.872300969511</v>
+        <v>1227.872300969507</v>
       </c>
       <c r="O7" t="n">
-        <v>984.9979938189909</v>
+        <v>984.9979938189869</v>
       </c>
       <c r="P7" t="n">
-        <v>694.6465823762865</v>
+        <v>694.6465823762824</v>
       </c>
       <c r="Q7" t="n">
-        <v>365.5160102292177</v>
+        <v>365.5160102292136</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T7" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="U7" t="n">
-        <v>348.9214477324598</v>
+        <v>65.12</v>
       </c>
       <c r="V7" t="n">
-        <v>547.7428406184058</v>
+        <v>65.12</v>
       </c>
       <c r="W7" t="n">
-        <v>719.6337588780832</v>
+        <v>65.12</v>
       </c>
       <c r="X7" t="n">
-        <v>794.048053503392</v>
+        <v>65.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>905.4573541824243</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="8">
@@ -4780,13 +4780,13 @@
         <v>641.9898070586958</v>
       </c>
       <c r="E8" t="n">
-        <v>233.5420397790304</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F8" t="n">
-        <v>228.6030208820488</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G8" t="n">
-        <v>224.8076953396081</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4795,22 +4795,22 @@
         <v>65.12</v>
       </c>
       <c r="J8" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>636.5532794332918</v>
+        <v>937.5543724554943</v>
       </c>
       <c r="L8" t="n">
-        <v>1442.413279433292</v>
+        <v>921.1921502332721</v>
       </c>
       <c r="M8" t="n">
-        <v>1426.05105721107</v>
+        <v>1426.051057211065</v>
       </c>
       <c r="N8" t="n">
-        <v>2035.360011169608</v>
+        <v>2035.360011169603</v>
       </c>
       <c r="O8" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169603</v>
       </c>
       <c r="P8" t="n">
         <v>2824.857788947385</v>
@@ -4822,22 +4822,22 @@
         <v>3256</v>
       </c>
       <c r="S8" t="n">
-        <v>2813.235960095906</v>
+        <v>2756.153365856239</v>
       </c>
       <c r="T8" t="n">
-        <v>2624.67476643069</v>
+        <v>2163.551768150619</v>
       </c>
       <c r="U8" t="n">
-        <v>2372.936083048255</v>
+        <v>1911.813084768184</v>
       </c>
       <c r="V8" t="n">
-        <v>2140.763331364595</v>
+        <v>1679.640333084523</v>
       </c>
       <c r="W8" t="n">
-        <v>1899.982042494951</v>
+        <v>1091.901234414142</v>
       </c>
       <c r="X8" t="n">
-        <v>1301.717564251852</v>
+        <v>897.6771602114478</v>
       </c>
       <c r="Y8" t="n">
         <v>785.2353090166939</v>
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527.4691155388109</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>527.4691155388109</v>
+        <v>931.509519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>527.4691155388109</v>
+        <v>580.0573105916365</v>
       </c>
       <c r="E9" t="n">
-        <v>394.1498342171994</v>
+        <v>233.9238790543509</v>
       </c>
       <c r="F9" t="n">
-        <v>394.1498342171994</v>
+        <v>65.12</v>
       </c>
       <c r="G9" t="n">
         <v>65.12</v>
@@ -4916,10 +4916,10 @@
         <v>951.5728927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>527.4691155388109</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.4691155388109</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>847.5758574435026</v>
+        <v>65.12</v>
       </c>
       <c r="C10" t="n">
-        <v>847.5758574435026</v>
+        <v>175.4088884311078</v>
       </c>
       <c r="D10" t="n">
-        <v>847.5758574435026</v>
+        <v>288.7280325561079</v>
       </c>
       <c r="E10" t="n">
-        <v>965.4047616549157</v>
+        <v>406.5569367675209</v>
       </c>
       <c r="F10" t="n">
-        <v>1089.765734246851</v>
+        <v>530.9179093594564</v>
       </c>
       <c r="G10" t="n">
-        <v>1089.765734246851</v>
+        <v>684.3244752463416</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.92480105819</v>
+        <v>853.8410604057392</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994273</v>
+        <v>1074.973939341822</v>
       </c>
       <c r="J10" t="n">
         <v>1436.057679994273</v>
@@ -4980,25 +4980,25 @@
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T10" t="n">
-        <v>290.445934252978</v>
+        <v>65.12</v>
       </c>
       <c r="U10" t="n">
-        <v>536.9971268912645</v>
+        <v>65.12</v>
       </c>
       <c r="V10" t="n">
-        <v>735.8185197772104</v>
+        <v>65.12</v>
       </c>
       <c r="W10" t="n">
-        <v>735.8185197772104</v>
+        <v>65.12</v>
       </c>
       <c r="X10" t="n">
-        <v>735.8185197772104</v>
+        <v>65.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>735.8185197772104</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="11">
@@ -5008,16 +5008,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>479.0732666493371</v>
+        <v>443.3049239128102</v>
       </c>
       <c r="C11" t="n">
-        <v>252.3312684240907</v>
+        <v>443.3049239128102</v>
       </c>
       <c r="D11" t="n">
-        <v>65.12</v>
+        <v>428.0017356715965</v>
       </c>
       <c r="E11" t="n">
-        <v>65.12</v>
+        <v>246.8266956646584</v>
       </c>
       <c r="F11" t="n">
         <v>65.12</v>
@@ -5032,52 +5032,52 @@
         <v>65.12</v>
       </c>
       <c r="J11" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>774.8263663478684</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1580.686366347868</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>1580.686366347869</v>
+        <v>1676.984308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>2193.906686122632</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O11" t="n">
-        <v>2193.906686122632</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="P11" t="n">
-        <v>2817.400904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="Q11" t="n">
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3229.860001183541</v>
+        <v>3256</v>
       </c>
       <c r="S11" t="n">
-        <v>3019.194435865494</v>
+        <v>2983.426093128967</v>
       </c>
       <c r="T11" t="n">
-        <v>2653.865565432601</v>
+        <v>2618.097222696074</v>
       </c>
       <c r="U11" t="n">
-        <v>2225.359205282489</v>
+        <v>2189.590862545962</v>
       </c>
       <c r="V11" t="n">
-        <v>1816.418776831151</v>
+        <v>1780.650434094625</v>
       </c>
       <c r="W11" t="n">
-        <v>1398.869811193831</v>
+        <v>1363.101468457304</v>
       </c>
       <c r="X11" t="n">
-        <v>1027.878060223459</v>
+        <v>992.1097174869324</v>
       </c>
       <c r="Y11" t="n">
-        <v>738.6685322610285</v>
+        <v>702.9001895245017</v>
       </c>
     </row>
     <row r="12">
@@ -5111,22 +5111,22 @@
         <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>215.7971006891144</v>
+        <v>419.6213981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>627.7399167834978</v>
+        <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1121.840378378698</v>
+        <v>1325.664675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1430.670920121557</v>
+        <v>1634.495217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1786.701204729125</v>
+        <v>1990.525502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2248.493656412844</v>
+        <v>2452.317953866594</v>
       </c>
       <c r="P12" t="n">
         <v>2583.773000882351</v>
@@ -5166,19 +5166,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>287.3106791955609</v>
+        <v>130.0769132900749</v>
       </c>
       <c r="C13" t="n">
-        <v>239.1033593490511</v>
+        <v>130.0769132900749</v>
       </c>
       <c r="D13" t="n">
-        <v>177.9556643434395</v>
+        <v>68.92921828446326</v>
       </c>
       <c r="E13" t="n">
-        <v>121.4092958212611</v>
+        <v>68.92921828446326</v>
       </c>
       <c r="F13" t="n">
-        <v>71.52762312657231</v>
+        <v>68.92921828446326</v>
       </c>
       <c r="G13" t="n">
         <v>68.92921828446326</v>
@@ -5193,49 +5193,49 @@
         <v>300.8366195885342</v>
       </c>
       <c r="K13" t="n">
-        <v>300.8366195885342</v>
+        <v>282.3639442919931</v>
       </c>
       <c r="L13" t="n">
-        <v>300.8366195885342</v>
+        <v>282.3639442919931</v>
       </c>
       <c r="M13" t="n">
-        <v>300.8366195885342</v>
+        <v>282.3639442919931</v>
       </c>
       <c r="N13" t="n">
-        <v>300.8366195885342</v>
+        <v>282.3639442919931</v>
       </c>
       <c r="O13" t="n">
-        <v>300.8366195885342</v>
+        <v>282.3639442919931</v>
       </c>
       <c r="P13" t="n">
-        <v>300.8366195885342</v>
+        <v>282.3639442919931</v>
       </c>
       <c r="Q13" t="n">
-        <v>300.8366195885342</v>
+        <v>282.3639442919931</v>
       </c>
       <c r="R13" t="n">
-        <v>300.8366195885342</v>
+        <v>282.3639442919931</v>
       </c>
       <c r="S13" t="n">
-        <v>300.8366195885342</v>
+        <v>143.6028536830482</v>
       </c>
       <c r="T13" t="n">
-        <v>315.6622987473391</v>
+        <v>158.4285328418531</v>
       </c>
       <c r="U13" t="n">
-        <v>388.9634913856257</v>
+        <v>231.7297254801397</v>
       </c>
       <c r="V13" t="n">
-        <v>414.5348842715717</v>
+        <v>257.3011183660857</v>
       </c>
       <c r="W13" t="n">
-        <v>413.1482076668144</v>
+        <v>255.9144417613284</v>
       </c>
       <c r="X13" t="n">
-        <v>413.1482076668144</v>
+        <v>255.9144417613284</v>
       </c>
       <c r="Y13" t="n">
-        <v>350.0518916572565</v>
+        <v>192.8181257517705</v>
       </c>
     </row>
     <row r="14">
@@ -5251,10 +5251,10 @@
         <v>452.9265620512006</v>
       </c>
       <c r="D14" t="n">
-        <v>379.1596842540801</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>379.1596842540801</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="F14" t="n">
         <v>223.7156148520479</v>
@@ -5275,16 +5275,16 @@
         <v>456.4291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>456.4291130376557</v>
+        <v>1262.289113037656</v>
       </c>
       <c r="M14" t="n">
-        <v>967.2779417665907</v>
+        <v>1773.137941766591</v>
       </c>
       <c r="N14" t="n">
-        <v>1580.498261541354</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="O14" t="n">
-        <v>2386.358261541354</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P14" t="n">
         <v>2817.400904947332</v>
@@ -5348,19 +5348,19 @@
         <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>222.6113981428639</v>
+        <v>387.1477067497204</v>
       </c>
       <c r="K15" t="n">
-        <v>411.8042142372473</v>
+        <v>824.8305228441038</v>
       </c>
       <c r="L15" t="n">
-        <v>931.6446758324474</v>
+        <v>1096.180984439304</v>
       </c>
       <c r="M15" t="n">
-        <v>1017.725217575307</v>
+        <v>1430.751526182163</v>
       </c>
       <c r="N15" t="n">
-        <v>1315.541810789732</v>
+        <v>1564.031810789731</v>
       </c>
       <c r="O15" t="n">
         <v>1803.074262473451</v>
@@ -5409,49 +5409,49 @@
         <v>283.9399739669084</v>
       </c>
       <c r="D16" t="n">
-        <v>249.054905223923</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="E16" t="n">
-        <v>249.054905223923</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="F16" t="n">
-        <v>249.054905223923</v>
+        <v>283.9399739669084</v>
       </c>
       <c r="G16" t="n">
-        <v>254.9514711108083</v>
+        <v>289.8365398537936</v>
       </c>
       <c r="H16" t="n">
-        <v>276.9580562702059</v>
+        <v>311.8431250131912</v>
       </c>
       <c r="I16" t="n">
-        <v>350.5809352062888</v>
+        <v>385.4660039492741</v>
       </c>
       <c r="J16" t="n">
-        <v>564.1546758587401</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="K16" t="n">
-        <v>564.1546758587401</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="L16" t="n">
-        <v>564.1546758587401</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="M16" t="n">
-        <v>564.1546758587401</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="N16" t="n">
-        <v>564.1546758587401</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>564.1546758587401</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>564.1546758587401</v>
+        <v>544.7556226521192</v>
       </c>
       <c r="Q16" t="n">
-        <v>564.1546758587401</v>
+        <v>65.12</v>
       </c>
       <c r="R16" t="n">
-        <v>83.74848597878952</v>
+        <v>65.12</v>
       </c>
       <c r="S16" t="n">
         <v>65.12</v>
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>880.1035184729978</v>
+        <v>879.6685602764463</v>
       </c>
       <c r="C17" t="n">
-        <v>707.906974793206</v>
+        <v>707.4720165966545</v>
       </c>
       <c r="D17" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.4503343338824</v>
+        <v>321.0153761373309</v>
       </c>
       <c r="G17" t="n">
         <v>195.4327865692196</v>
@@ -5521,10 +5521,10 @@
         <v>3096.064627889222</v>
       </c>
       <c r="O17" t="n">
-        <v>3256</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="P17" t="n">
-        <v>3256</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5536,22 +5536,22 @@
         <v>3037.971547674421</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V17" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W17" t="n">
-        <v>1636.263699381128</v>
+        <v>1635.828741184576</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y17" t="n">
-        <v>1085.153329539235</v>
+        <v>1084.718371342683</v>
       </c>
     </row>
     <row r="18">
@@ -5585,22 +5585,22 @@
         <v>126.374877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>250.3313981428639</v>
+        <v>526.5413981428638</v>
       </c>
       <c r="K18" t="n">
-        <v>439.5242142372473</v>
+        <v>869.8480986016793</v>
       </c>
       <c r="L18" t="n">
-        <v>710.8746758324473</v>
+        <v>1141.198560196879</v>
       </c>
       <c r="M18" t="n">
-        <v>796.9552175753066</v>
+        <v>1227.279101939739</v>
       </c>
       <c r="N18" t="n">
-        <v>930.2355021828749</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O18" t="n">
-        <v>1323.391838231026</v>
+        <v>1599.601838231026</v>
       </c>
       <c r="P18" t="n">
         <v>1712.131182700533</v>
@@ -5679,13 +5679,13 @@
         <v>859.3027230120967</v>
       </c>
       <c r="O19" t="n">
-        <v>494.2061936393544</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>494.2061936393544</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q19" t="n">
-        <v>494.2061936393544</v>
+        <v>407.9499286428058</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5728,10 +5728,10 @@
         <v>574.8062027180183</v>
       </c>
       <c r="E20" t="n">
-        <v>448.1766172565348</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F20" t="n">
-        <v>321.0153761373309</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G20" t="n">
         <v>195.4327865692196</v>
@@ -5743,25 +5743,25 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>456.4291130376557</v>
+        <v>177.7653900957659</v>
       </c>
       <c r="K20" t="n">
-        <v>1166.135479385524</v>
+        <v>887.4717564436343</v>
       </c>
       <c r="L20" t="n">
-        <v>1326.070851496302</v>
+        <v>1693.331756443634</v>
       </c>
       <c r="M20" t="n">
-        <v>1836.919680225237</v>
+        <v>2204.180585172569</v>
       </c>
       <c r="N20" t="n">
-        <v>2450.14</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>3256</v>
@@ -5822,19 +5822,19 @@
         <v>126.374877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>526.5413981428638</v>
+        <v>404.4452825072959</v>
       </c>
       <c r="K21" t="n">
-        <v>869.8480986016793</v>
+        <v>593.6380986016793</v>
       </c>
       <c r="L21" t="n">
-        <v>1141.198560196879</v>
+        <v>864.9885601968793</v>
       </c>
       <c r="M21" t="n">
-        <v>1227.279101939739</v>
+        <v>951.0691019397386</v>
       </c>
       <c r="N21" t="n">
-        <v>1360.559386547307</v>
+        <v>1084.349386547307</v>
       </c>
       <c r="O21" t="n">
         <v>1599.601838231026</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>417.6452712026824</v>
+        <v>414.3442160506673</v>
       </c>
       <c r="C22" t="n">
-        <v>423.8572770211181</v>
+        <v>420.5562218691031</v>
       </c>
       <c r="D22" t="n">
-        <v>423.8572770211181</v>
+        <v>413.953981408946</v>
       </c>
       <c r="E22" t="n">
-        <v>421.8563630443944</v>
+        <v>413.953981408946</v>
       </c>
       <c r="F22" t="n">
-        <v>426.4273356363299</v>
+        <v>418.5249540008816</v>
       </c>
       <c r="G22" t="n">
-        <v>460.0439015232151</v>
+        <v>452.1415198877668</v>
       </c>
       <c r="H22" t="n">
-        <v>509.7704866826127</v>
+        <v>501.8681050471644</v>
       </c>
       <c r="I22" t="n">
-        <v>611.1133656186956</v>
+        <v>603.2109839832474</v>
       </c>
       <c r="J22" t="n">
-        <v>852.407106271147</v>
+        <v>844.5047246356987</v>
       </c>
       <c r="K22" t="n">
-        <v>842.7901630376691</v>
+        <v>834.8877814022209</v>
       </c>
       <c r="L22" t="n">
-        <v>842.7901630376691</v>
+        <v>834.8877814022209</v>
       </c>
       <c r="M22" t="n">
-        <v>842.7901630376691</v>
+        <v>834.8877814022209</v>
       </c>
       <c r="N22" t="n">
-        <v>842.7901630376691</v>
+        <v>834.8877814022209</v>
       </c>
       <c r="O22" t="n">
-        <v>477.6936336649268</v>
+        <v>834.8877814022209</v>
       </c>
       <c r="P22" t="n">
-        <v>65.12</v>
+        <v>834.8877814022209</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.12</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="R22" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S22" t="n">
         <v>65.12</v>
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>880.1035184729978</v>
+        <v>879.6685602764463</v>
       </c>
       <c r="C23" t="n">
-        <v>707.906974793206</v>
+        <v>707.4720165966545</v>
       </c>
       <c r="D23" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180183</v>
       </c>
       <c r="E23" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F23" t="n">
-        <v>321.4503343338824</v>
+        <v>321.0153761373309</v>
       </c>
       <c r="G23" t="n">
         <v>195.4327865692196</v>
@@ -5992,7 +5992,7 @@
         <v>967.2779417665907</v>
       </c>
       <c r="N23" t="n">
-        <v>1205.680904947332</v>
+        <v>1580.498261541354</v>
       </c>
       <c r="O23" t="n">
         <v>2011.540904947332</v>
@@ -6007,25 +6007,25 @@
         <v>3256</v>
       </c>
       <c r="S23" t="n">
-        <v>3038.406505870973</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V23" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W23" t="n">
-        <v>1636.263699381128</v>
+        <v>1635.828741184576</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y23" t="n">
-        <v>1085.153329539235</v>
+        <v>1084.718371342683</v>
       </c>
     </row>
     <row r="24">
@@ -6059,13 +6059,13 @@
         <v>126.374877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>404.4452825072959</v>
+        <v>526.5413981428638</v>
       </c>
       <c r="K24" t="n">
-        <v>593.6380986016793</v>
+        <v>869.8480986016793</v>
       </c>
       <c r="L24" t="n">
-        <v>864.9885601968795</v>
+        <v>1141.198560196879</v>
       </c>
       <c r="M24" t="n">
         <v>1227.279101939739</v>
@@ -6114,52 +6114,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>405.793354586564</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C25" t="n">
-        <v>412.0053604049997</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D25" t="n">
-        <v>405.4031199448427</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E25" t="n">
-        <v>403.4022059681189</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F25" t="n">
-        <v>407.9731785600544</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G25" t="n">
-        <v>441.5897444469397</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H25" t="n">
-        <v>491.3163296063373</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I25" t="n">
-        <v>592.6592085424202</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J25" t="n">
-        <v>833.9529491948715</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K25" t="n">
-        <v>824.3360059613937</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L25" t="n">
-        <v>678.3283007515157</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M25" t="n">
-        <v>434.2559660014653</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N25" t="n">
-        <v>139.1195263330967</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O25" t="n">
-        <v>65.12</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>65.12</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.12</v>
+        <v>407.9499286428058</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6183,7 +6183,7 @@
         <v>422.5399739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>413.989112502805</v>
+        <v>422.5399739669084</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253.1649250963515</v>
+        <v>891.0677024002771</v>
       </c>
       <c r="C26" t="n">
-        <v>61.84</v>
+        <v>664.3257041750308</v>
       </c>
       <c r="D26" t="n">
-        <v>61.84</v>
+        <v>608.9679390894501</v>
       </c>
       <c r="E26" t="n">
-        <v>61.84</v>
+        <v>608.9679390894501</v>
       </c>
       <c r="F26" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="G26" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6220,19 +6220,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="M26" t="n">
-        <v>1673.704308114459</v>
+        <v>963.9979417665908</v>
       </c>
       <c r="N26" t="n">
-        <v>2286.924627889222</v>
+        <v>1577.218261541354</v>
       </c>
       <c r="O26" t="n">
-        <v>2286.924627889222</v>
+        <v>1888.130904947305</v>
       </c>
       <c r="P26" t="n">
         <v>2653.400904947332</v>
@@ -6244,25 +6244,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>2793.286094312508</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="T26" t="n">
-        <v>2427.957223879615</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="U26" t="n">
-        <v>1999.450863729503</v>
+        <v>2637.353641033429</v>
       </c>
       <c r="V26" t="n">
-        <v>1590.510435278166</v>
+        <v>2228.413212582092</v>
       </c>
       <c r="W26" t="n">
-        <v>1172.961469640845</v>
+        <v>1810.864246944771</v>
       </c>
       <c r="X26" t="n">
-        <v>801.9697186704736</v>
+        <v>1439.872495974399</v>
       </c>
       <c r="Y26" t="n">
-        <v>512.760190708043</v>
+        <v>1150.662968011969</v>
       </c>
     </row>
     <row r="27">
@@ -6293,22 +6293,22 @@
         <v>61.84</v>
       </c>
       <c r="I27" t="n">
-        <v>61.84</v>
+        <v>69.63487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>408.546520175299</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>820.4893362696823</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1314.589797864882</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1623.420339607742</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.421204729126</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O27" t="n">
         <v>2245.213656412845</v>
@@ -6351,55 +6351,55 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="G28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="H28" t="n">
-        <v>151.4812391589797</v>
+        <v>170.342369793817</v>
       </c>
       <c r="I28" t="n">
-        <v>199.3641180950626</v>
+        <v>218.2252487298999</v>
       </c>
       <c r="J28" t="n">
-        <v>387.1978587475139</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="K28" t="n">
-        <v>387.1978587475139</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>387.1978587475139</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="M28" t="n">
-        <v>387.1978587475139</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="N28" t="n">
-        <v>387.1978587475139</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="O28" t="n">
-        <v>387.1978587475139</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="P28" t="n">
-        <v>387.1978587475139</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="Q28" t="n">
-        <v>387.1978587475139</v>
+        <v>61.84</v>
       </c>
       <c r="R28" t="n">
-        <v>200.6010906089449</v>
+        <v>61.84</v>
       </c>
       <c r="S28" t="n">
         <v>61.84</v>
@@ -6417,10 +6417,10 @@
         <v>174.1515880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>288.5819982252464</v>
+        <v>253.1649250963515</v>
       </c>
       <c r="C29" t="n">
         <v>61.84</v>
@@ -6457,22 +6457,22 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K29" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>1928.125479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="M29" t="n">
-        <v>2438.974308114459</v>
+        <v>963.9979417665908</v>
       </c>
       <c r="N29" t="n">
-        <v>3052.194627889222</v>
+        <v>1577.218261541354</v>
       </c>
       <c r="O29" t="n">
-        <v>3052.194627889222</v>
+        <v>1888.130904947298</v>
       </c>
       <c r="P29" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>3092</v>
@@ -6533,22 +6533,22 @@
         <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>416.3413981428639</v>
+        <v>212.5171006891147</v>
       </c>
       <c r="K30" t="n">
-        <v>828.2842142372474</v>
+        <v>624.4599167834981</v>
       </c>
       <c r="L30" t="n">
-        <v>1322.384675832448</v>
+        <v>1118.560378378698</v>
       </c>
       <c r="M30" t="n">
-        <v>1631.215217575307</v>
+        <v>1427.390920121557</v>
       </c>
       <c r="N30" t="n">
-        <v>1987.245502182875</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2449.037953866594</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P30" t="n">
         <v>2580.493000882351</v>
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>174.1515880782802</v>
+        <v>126.7969132900749</v>
       </c>
       <c r="C31" t="n">
-        <v>174.1515880782802</v>
+        <v>126.7969132900749</v>
       </c>
       <c r="D31" t="n">
-        <v>174.1515880782802</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="E31" t="n">
-        <v>174.1515880782802</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="F31" t="n">
-        <v>174.1515880782802</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="G31" t="n">
-        <v>174.1515880782802</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="H31" t="n">
-        <v>170.342369793817</v>
+        <v>61.84</v>
       </c>
       <c r="I31" t="n">
-        <v>218.2252487298999</v>
+        <v>109.7228789360829</v>
       </c>
       <c r="J31" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="K31" t="n">
-        <v>406.0589893823512</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="L31" t="n">
-        <v>406.0589893823512</v>
+        <v>279.0839442919931</v>
       </c>
       <c r="M31" t="n">
-        <v>406.0589893823512</v>
+        <v>279.0839442919931</v>
       </c>
       <c r="N31" t="n">
-        <v>406.0589893823512</v>
+        <v>279.0839442919931</v>
       </c>
       <c r="O31" t="n">
-        <v>406.0589893823512</v>
+        <v>279.0839442919931</v>
       </c>
       <c r="P31" t="n">
-        <v>406.0589893823512</v>
+        <v>279.0839442919931</v>
       </c>
       <c r="Q31" t="n">
-        <v>406.0589893823512</v>
+        <v>279.0839442919931</v>
       </c>
       <c r="R31" t="n">
-        <v>61.84</v>
+        <v>279.0839442919931</v>
       </c>
       <c r="S31" t="n">
-        <v>61.84</v>
+        <v>140.3228536830482</v>
       </c>
       <c r="T31" t="n">
-        <v>76.66567915880486</v>
+        <v>155.1485328418531</v>
       </c>
       <c r="U31" t="n">
-        <v>149.9668717970915</v>
+        <v>228.4497254801397</v>
       </c>
       <c r="V31" t="n">
-        <v>175.5382646830375</v>
+        <v>254.0211183660857</v>
       </c>
       <c r="W31" t="n">
-        <v>174.1515880782802</v>
+        <v>252.6344417613284</v>
       </c>
       <c r="X31" t="n">
-        <v>174.1515880782802</v>
+        <v>252.6344417613284</v>
       </c>
       <c r="Y31" t="n">
-        <v>174.1515880782802</v>
+        <v>189.5381257517705</v>
       </c>
     </row>
     <row r="32">
@@ -6670,19 +6670,19 @@
         <v>812.6382572461436</v>
       </c>
       <c r="C32" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D32" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E32" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F32" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G32" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H32" t="n">
         <v>61.84</v>
@@ -6694,22 +6694,22 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K32" t="n">
-        <v>430.9405883765107</v>
+        <v>1155.05686870287</v>
       </c>
       <c r="L32" t="n">
-        <v>415.4025075684297</v>
+        <v>1139.518787894789</v>
       </c>
       <c r="M32" t="n">
-        <v>921.0855559603634</v>
+        <v>1645.201836286723</v>
       </c>
       <c r="N32" t="n">
-        <v>1531.218651333042</v>
+        <v>2255.334931659402</v>
       </c>
       <c r="O32" t="n">
-        <v>1894.763647533204</v>
+        <v>3020.604931659443</v>
       </c>
       <c r="P32" t="n">
-        <v>2660.033647533245</v>
+        <v>3092</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
@@ -6767,25 +6767,25 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>71.63058051381552</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>195.5871006891145</v>
+        <v>483.6771006891146</v>
       </c>
       <c r="K33" t="n">
-        <v>384.7799167834979</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L33" t="n">
-        <v>656.130378378698</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>742.2109201215573</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>875.4912047291256</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>1114.533656412844</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P33" t="n">
         <v>1515.153000882351</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486.0066123122566</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C34" t="n">
         <v>504.0986181306923</v>
@@ -6837,40 +6837,40 @@
         <v>519.4266664671054</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590646</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459498</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053474</v>
       </c>
       <c r="I34" t="n">
-        <v>756.2036690414067</v>
+        <v>756.2036690414303</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693882</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.83184363075</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.83184363075</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.83184363075</v>
       </c>
       <c r="N34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.83184363075</v>
       </c>
       <c r="O34" t="n">
-        <v>1011.831843630726</v>
+        <v>658.8565263792198</v>
       </c>
       <c r="P34" t="n">
-        <v>941.0737317239891</v>
+        <v>501.0715822480788</v>
       </c>
       <c r="Q34" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="R34" t="n">
         <v>61.84</v>
@@ -6894,7 +6894,7 @@
         <v>478.6599739669085</v>
       </c>
       <c r="Y34" t="n">
-        <v>482.1592746459644</v>
+        <v>482.1592746459407</v>
       </c>
     </row>
     <row r="35">
@@ -6922,25 +6922,25 @@
         <v>188.5735859484259</v>
       </c>
       <c r="H35" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I35" t="n">
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>61.84</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>61.84</v>
+        <v>430.0181114556215</v>
       </c>
       <c r="L35" t="n">
-        <v>639.3486799492955</v>
+        <v>415.4025075684356</v>
       </c>
       <c r="M35" t="n">
-        <v>1145.031728341229</v>
+        <v>921.0855559603692</v>
       </c>
       <c r="N35" t="n">
-        <v>1129.493647533147</v>
+        <v>1531.218651333048</v>
       </c>
       <c r="O35" t="n">
         <v>1894.763647533196</v>
@@ -7013,16 +7013,16 @@
         <v>448.1242142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>944.220378378698</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M36" t="n">
-        <v>1030.300920121557</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N36" t="n">
-        <v>1163.581204729126</v>
+        <v>938.8355021828751</v>
       </c>
       <c r="O36" t="n">
-        <v>1402.623656412844</v>
+        <v>1177.877953866594</v>
       </c>
       <c r="P36" t="n">
         <v>1515.153000882351</v>
@@ -7098,19 +7098,19 @@
         <v>1011.831843630703</v>
       </c>
       <c r="N37" t="n">
-        <v>728.8166160835463</v>
+        <v>815.2677387952449</v>
       </c>
       <c r="O37" t="n">
-        <v>728.8166160835463</v>
+        <v>462.2924215437147</v>
       </c>
       <c r="P37" t="n">
-        <v>728.8166160835463</v>
+        <v>61.84</v>
       </c>
       <c r="Q37" t="n">
-        <v>573.9365734181883</v>
+        <v>61.84</v>
       </c>
       <c r="R37" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7141,43 +7141,43 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D38" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E38" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F38" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G38" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H38" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I38" t="n">
         <v>61.84</v>
       </c>
       <c r="J38" t="n">
-        <v>61.84</v>
+        <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>771.3406764391792</v>
+        <v>810.0236653847411</v>
       </c>
       <c r="L38" t="n">
-        <v>1536.610676439179</v>
+        <v>794.4855845766601</v>
       </c>
       <c r="M38" t="n">
-        <v>2042.293724831113</v>
+        <v>1300.168632968594</v>
       </c>
       <c r="N38" t="n">
-        <v>2652.426820203791</v>
+        <v>1910.301728341272</v>
       </c>
       <c r="O38" t="n">
         <v>2675.571728341328</v>
@@ -7189,28 +7189,28 @@
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S38" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T38" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U38" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V38" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W38" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X38" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y38" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="39">
@@ -7244,22 +7244,22 @@
         <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>258.9313981428639</v>
+        <v>483.6771006891146</v>
       </c>
       <c r="K39" t="n">
-        <v>448.1242142372473</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L39" t="n">
-        <v>719.4746758324475</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M39" t="n">
-        <v>805.5552175753068</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N39" t="n">
-        <v>938.8355021828751</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O39" t="n">
-        <v>1177.877953866594</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P39" t="n">
         <v>1515.153000882351</v>
@@ -7302,40 +7302,40 @@
         <v>486.0066123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306959</v>
       </c>
       <c r="D40" t="n">
-        <v>509.5077622556687</v>
+        <v>509.507762255696</v>
       </c>
       <c r="E40" t="n">
-        <v>519.4266664670818</v>
+        <v>519.426666467109</v>
       </c>
       <c r="F40" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590718</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459571</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053547</v>
       </c>
       <c r="I40" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414376</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693889</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630757</v>
       </c>
       <c r="L40" t="n">
-        <v>877.945350542037</v>
+        <v>877.9453505420915</v>
       </c>
       <c r="M40" t="n">
-        <v>645.9942279131988</v>
+        <v>645.9942279132533</v>
       </c>
       <c r="N40" t="n">
-        <v>362.9790003660423</v>
+        <v>362.9790003660968</v>
       </c>
       <c r="O40" t="n">
         <v>61.84</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>144.0740160054425</v>
+        <v>1082.995610687127</v>
       </c>
       <c r="C41" t="n">
-        <v>144.0740160054425</v>
+        <v>844.1324003406687</v>
       </c>
       <c r="D41" t="n">
-        <v>144.0740160054425</v>
+        <v>644.7999197953659</v>
       </c>
       <c r="E41" t="n">
-        <v>61.84</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="F41" t="n">
-        <v>61.84</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="G41" t="n">
-        <v>61.84</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7402,22 +7402,22 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K41" t="n">
-        <v>453.1491130376558</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L41" t="n">
-        <v>612.0120762182711</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="M41" t="n">
-        <v>1122.860904947206</v>
+        <v>1282.395195076803</v>
       </c>
       <c r="N41" t="n">
-        <v>1122.860904947206</v>
+        <v>1895.615514851567</v>
       </c>
       <c r="O41" t="n">
-        <v>1888.130904947269</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>2653.400904947332</v>
@@ -7429,25 +7429,25 @@
         <v>3053.738789062329</v>
       </c>
       <c r="S41" t="n">
-        <v>2769.043670070084</v>
+        <v>2995.621214747541</v>
       </c>
       <c r="T41" t="n">
-        <v>2391.593587515979</v>
+        <v>2618.171132193436</v>
       </c>
       <c r="U41" t="n">
-        <v>1950.966015244655</v>
+        <v>2618.171132193436</v>
       </c>
       <c r="V41" t="n">
-        <v>1529.904374672105</v>
+        <v>2197.109491620887</v>
       </c>
       <c r="W41" t="n">
-        <v>1100.234196913573</v>
+        <v>1767.439313862354</v>
       </c>
       <c r="X41" t="n">
-        <v>717.1212338219889</v>
+        <v>1384.32635077077</v>
       </c>
       <c r="Y41" t="n">
-        <v>415.7904937383461</v>
+        <v>1082.995610687127</v>
       </c>
     </row>
     <row r="42">
@@ -7484,19 +7484,19 @@
         <v>396.666520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>796.7293362696823</v>
+        <v>742.8711724895873</v>
       </c>
       <c r="L42" t="n">
-        <v>1278.949797864882</v>
+        <v>1225.091634084787</v>
       </c>
       <c r="M42" t="n">
-        <v>1575.900339607742</v>
+        <v>1522.042175827647</v>
       </c>
       <c r="N42" t="n">
-        <v>1920.05062421531</v>
+        <v>1866.192460435215</v>
       </c>
       <c r="O42" t="n">
-        <v>2369.963075899029</v>
+        <v>2316.104912118933</v>
       </c>
       <c r="P42" t="n">
         <v>2639.50425658844</v>
@@ -7505,19 +7505,19 @@
         <v>2679.025784148865</v>
       </c>
       <c r="R42" t="n">
-        <v>2341.375483853532</v>
+        <v>2480.230476522543</v>
       </c>
       <c r="S42" t="n">
-        <v>2085.250231364026</v>
+        <v>2224.105224033037</v>
       </c>
       <c r="T42" t="n">
-        <v>1890.949458417042</v>
+        <v>2029.804451086053</v>
       </c>
       <c r="U42" t="n">
-        <v>1701.848084921904</v>
+        <v>1840.703077590915</v>
       </c>
       <c r="V42" t="n">
-        <v>1498.301956445621</v>
+        <v>1637.156949114632</v>
       </c>
       <c r="W42" t="n">
         <v>1415.567915872381</v>
@@ -7560,37 +7560,37 @@
         <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="K43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="L43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="M43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="N43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="O43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="P43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="R43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="S43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>91.27831913164476</v>
+        <v>61.84</v>
       </c>
       <c r="U43" t="n">
         <v>91.27831913164476</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>844.2405952384764</v>
+        <v>61.84</v>
       </c>
       <c r="C44" t="n">
-        <v>844.2405952384764</v>
+        <v>61.84</v>
       </c>
       <c r="D44" t="n">
-        <v>618.6454884305474</v>
+        <v>61.84</v>
       </c>
       <c r="E44" t="n">
-        <v>618.6454884305474</v>
+        <v>61.84</v>
       </c>
       <c r="F44" t="n">
-        <v>398.5549543820506</v>
+        <v>61.84</v>
       </c>
       <c r="G44" t="n">
-        <v>179.6081136880948</v>
+        <v>61.84</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7639,19 +7639,19 @@
         <v>61.84</v>
       </c>
       <c r="J44" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K44" t="n">
-        <v>453.1491130376558</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L44" t="n">
-        <v>764.0617564435566</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="M44" t="n">
-        <v>1274.910585172492</v>
+        <v>1282.395195076803</v>
       </c>
       <c r="N44" t="n">
-        <v>1888.130904947255</v>
+        <v>1895.615514851567</v>
       </c>
       <c r="O44" t="n">
         <v>2653.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3027.476162799703</v>
+        <v>3092</v>
       </c>
       <c r="S44" t="n">
-        <v>3027.476162799703</v>
+        <v>2870.648037903025</v>
       </c>
       <c r="T44" t="n">
-        <v>2623.763453982971</v>
+        <v>2466.935329086294</v>
       </c>
       <c r="U44" t="n">
-        <v>2156.873255449021</v>
+        <v>2000.045130552344</v>
       </c>
       <c r="V44" t="n">
-        <v>1709.548988613845</v>
+        <v>1552.720863717168</v>
       </c>
       <c r="W44" t="n">
-        <v>1253.616184592686</v>
+        <v>1096.788059696009</v>
       </c>
       <c r="X44" t="n">
-        <v>844.2405952384764</v>
+        <v>687.412470341799</v>
       </c>
       <c r="Y44" t="n">
-        <v>844.2405952384764</v>
+        <v>359.8191039955299</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>430.69251033795</v>
+        <v>1028.890452379605</v>
       </c>
       <c r="C45" t="n">
-        <v>254.8340129182335</v>
+        <v>853.031954959888</v>
       </c>
       <c r="D45" t="n">
-        <v>92.27069281954398</v>
+        <v>690.4686348611986</v>
       </c>
       <c r="E45" t="n">
-        <v>92.27069281954398</v>
+        <v>533.2240922128019</v>
       </c>
       <c r="F45" t="n">
-        <v>92.27069281954398</v>
+        <v>379.04606964929</v>
       </c>
       <c r="G45" t="n">
-        <v>92.27069281954398</v>
+        <v>238.9051243209795</v>
       </c>
       <c r="H45" t="n">
         <v>92.27069281954398</v>
@@ -7718,52 +7718,52 @@
         <v>61.84</v>
       </c>
       <c r="J45" t="n">
-        <v>370.9265201752989</v>
+        <v>264.7932046494833</v>
       </c>
       <c r="K45" t="n">
-        <v>745.2493362696823</v>
+        <v>639.1160207438668</v>
       </c>
       <c r="L45" t="n">
-        <v>1201.729797864882</v>
+        <v>1095.596482339067</v>
       </c>
       <c r="M45" t="n">
-        <v>1472.940339607742</v>
+        <v>1366.807024081926</v>
       </c>
       <c r="N45" t="n">
-        <v>1791.35062421531</v>
+        <v>1685.217308689495</v>
       </c>
       <c r="O45" t="n">
-        <v>2215.523075899029</v>
+        <v>2109.389760373213</v>
       </c>
       <c r="P45" t="n">
-        <v>2367.613069551632</v>
+        <v>2407.04910484272</v>
       </c>
       <c r="Q45" t="n">
-        <v>2367.613069551632</v>
+        <v>2407.04910484272</v>
       </c>
       <c r="R45" t="n">
-        <v>2003.700142993673</v>
+        <v>2343.930332204927</v>
       </c>
       <c r="S45" t="n">
-        <v>1745.732390163273</v>
+        <v>2343.930332204927</v>
       </c>
       <c r="T45" t="n">
-        <v>1525.168990953663</v>
+        <v>2123.366932995317</v>
       </c>
       <c r="U45" t="n">
-        <v>1309.804991195898</v>
+        <v>1908.002933237553</v>
       </c>
       <c r="V45" t="n">
-        <v>1079.996236456989</v>
+        <v>1678.194178498644</v>
       </c>
       <c r="W45" t="n">
-        <v>1079.996236456989</v>
+        <v>1678.194178498644</v>
       </c>
       <c r="X45" t="n">
-        <v>844.7813481283146</v>
+        <v>1442.979290169969</v>
       </c>
       <c r="Y45" t="n">
-        <v>630.2445877584819</v>
+        <v>1228.442529800137</v>
       </c>
     </row>
     <row r="46">
@@ -7773,22 +7773,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="C46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="D46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="E46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="F46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="G46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="H46" t="n">
         <v>61.84</v>
@@ -7797,52 +7797,52 @@
         <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="K46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="L46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="M46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="N46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="O46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="P46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="Q46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="R46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="S46" t="n">
-        <v>131.3795169037194</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="T46" t="n">
-        <v>108.1223790186106</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="U46" t="n">
-        <v>143.8035716568973</v>
+        <v>74.13324264264263</v>
       </c>
       <c r="V46" t="n">
-        <v>143.8035716568973</v>
+        <v>61.84</v>
       </c>
       <c r="W46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="X46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="Y46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>51.24160624509022</v>
+        <v>214.2751174529344</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P2" t="n">
-        <v>395.5658246095669</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q2" t="n">
-        <v>189.0212843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,13 +8201,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>814</v>
+        <v>589.8643001499323</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
@@ -8216,10 +8216,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P5" t="n">
-        <v>113.9633473726471</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q5" t="n">
         <v>189.0212843274853</v>
@@ -8438,25 +8438,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>581.9175466389589</v>
+        <v>500.8454983898731</v>
       </c>
       <c r="L8" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406860149</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>630.0792002676517</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>334.3735652474629</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,10 +8927,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>884.2478695740924</v>
+        <v>505.644479075081</v>
       </c>
       <c r="P14" t="n">
-        <v>435.68366954167</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>231.79875049407</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>334.3735652474629</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>148.8262285640457</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>161.5508809199773</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9635,10 +9635,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>718.0600319897761</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>884.2478695740924</v>
+        <v>505.6444790750808</v>
       </c>
       <c r="P23" t="n">
         <v>814.2870600406815</v>
@@ -9863,7 +9863,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9875,10 +9875,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>384.301044731619</v>
       </c>
       <c r="P26" t="n">
-        <v>370.4651176751361</v>
+        <v>773.287060040709</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,10 +10100,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,13 +10112,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>384.3010447316117</v>
       </c>
       <c r="P29" t="n">
-        <v>40.49450661722447</v>
+        <v>773.2870600407163</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,7 +10337,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>445.5401158122531</v>
+        <v>843.2478695741345</v>
       </c>
       <c r="P32" t="n">
-        <v>773.2870600407235</v>
+        <v>86.35087769783395</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>188.2053843274865</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,22 +10571,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>50.42570624509131</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>14.46944784831313</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>587.1162931498027</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>843.2478695741418</v>
+        <v>445.5401158122404</v>
       </c>
       <c r="P35" t="n">
         <v>773.2870600407308</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>50.42570624509142</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>716.8751175230994</v>
+        <v>375.2922462381518</v>
       </c>
       <c r="L38" t="n">
-        <v>772.9999999999998</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,7 +10823,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>108.5440286302554</v>
+        <v>843.247869574149</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11045,25 +11045,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>160.4676395763792</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>843.2478695741563</v>
+        <v>835.6876575496134</v>
       </c>
       <c r="P41" t="n">
-        <v>773.2870600407454</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>314.0531751574757</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11297,7 +11297,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>843.2478695741709</v>
+        <v>835.6876575496134</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
@@ -22700,10 +22700,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.662449696453351</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>29.21007785422643</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>29.21007785422552</v>
+        <v>29.21007785422961</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>5.662449696446146</v>
+        <v>5.662449696445918</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23226,16 +23226,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>170.1889993810482</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>178.7573722870162</v>
@@ -23271,10 +23271,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>61.28925813745602</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23384,19 +23384,19 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>17.47145204784207</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>63.52077380114304</v>
+        <v>45.23282525756732</v>
       </c>
       <c r="L13" t="n">
         <v>198.5476281577792</v>
@@ -23432,7 +23432,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23466,13 +23466,13 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>86.30994672070054</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>86.30994672070055</v>
       </c>
       <c r="G14" t="n">
         <v>152.7573722870162</v>
@@ -23624,7 +23624,7 @@
         <v>21.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E16" t="n">
         <v>29.98090483695654</v>
@@ -23660,16 +23660,16 @@
         <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>382.7066165981673</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>92.93127858385381</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.4306086145860206</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23751,7 +23751,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4306086145855375</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -23894,16 +23894,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>22.80679627819023</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -23943,13 +23943,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.4306086145860064</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4306086145860206</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -24092,16 +24092,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.268044600494865</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -24131,19 +24131,19 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>215.7447705214059</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.4306086145860206</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.430608614585708</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24329,16 +24329,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24356,28 +24356,28 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>288.1860330092492</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24398,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="26">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>35.06290239760591</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>130.5349683051249</v>
       </c>
       <c r="E26" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,10 +24459,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24611,13 +24611,13 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370703</v>
       </c>
       <c r="R28" t="n">
-        <v>316.8713275239677</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24632,7 +24632,7 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
         <v>62.46535284946236</v>
@@ -24645,10 +24645,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>35.06290239760588</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>35.06290239760591</v>
       </c>
       <c r="D29" t="n">
         <v>185.3391557398498</v>
@@ -24803,13 +24803,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>55.98090483695654</v>
@@ -24833,7 +24833,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L31" t="n">
-        <v>198.5476281577792</v>
+        <v>180.2596796142035</v>
       </c>
       <c r="M31" t="n">
         <v>295.6316114025499</v>
@@ -24851,10 +24851,10 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24872,7 +24872,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -25079,16 +25079,16 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>326.3973665406075</v>
+        <v>240.2408026384479</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>71.37347970285543</v>
@@ -25313,22 +25313,22 @@
         <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>85.5866114845816</v>
       </c>
       <c r="O37" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>281.5080241868936</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25553,7 +25553,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>51.3179537166331</v>
+        <v>51.31795371657904</v>
       </c>
       <c r="P40" t="n">
         <v>396.4478973282775</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>197.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>109.9516137614806</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,13 +25644,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>224.311769230683</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>137.4664427423205</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>137.4664427423205</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>294.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>104.4192261523135</v>
+        <v>221.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,10 +25878,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>88.70972532631805</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>324.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -25918,16 +25918,16 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>155.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>152.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>138.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>145.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>297.7862123809642</v>
       </c>
       <c r="S45" t="n">
-        <v>24.1759246625148</v>
+        <v>279.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26048,10 +26048,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>12.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>838100.8565553334</v>
+        <v>838100.8565553332</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1561839.555672187</v>
+        <v>1561839.555672186</v>
       </c>
     </row>
     <row r="4">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2931872.753357158</v>
+        <v>2931872.753357157</v>
       </c>
     </row>
     <row r="6">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5708788.291664338</v>
+        <v>5708788.291664337</v>
       </c>
     </row>
     <row r="10">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6986248.91137947</v>
+        <v>6986248.911379471</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7692311.287326631</v>
+        <v>7692311.287326634</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8397276.87151074</v>
+        <v>8397276.871510744</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9102242.455694856</v>
+        <v>9102242.45569486</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9722221.807536924</v>
+        <v>9722221.807536926</v>
       </c>
     </row>
     <row r="16">
@@ -26269,16 +26269,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1478944.29819531</v>
+      </c>
+      <c r="C2" t="n">
         <v>1478944.298195309</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1478944.29819531</v>
       </c>
-      <c r="D2" t="n">
-        <v>1478944.298195309</v>
-      </c>
       <c r="E2" t="n">
-        <v>1323084.101908757</v>
+        <v>1323084.101908756</v>
       </c>
       <c r="F2" t="n">
         <v>1377041.660956641</v>
@@ -26290,22 +26290,22 @@
         <v>1432508.291281669</v>
       </c>
       <c r="I2" t="n">
-        <v>1432508.29128167</v>
+        <v>1432508.291281669</v>
       </c>
       <c r="J2" t="n">
+        <v>1308202.281724756</v>
+      </c>
+      <c r="K2" t="n">
         <v>1308202.281724757</v>
       </c>
-      <c r="K2" t="n">
-        <v>1308202.281724756</v>
-      </c>
       <c r="L2" t="n">
+        <v>1440581.845941443</v>
+      </c>
+      <c r="M2" t="n">
         <v>1440581.845941442</v>
       </c>
-      <c r="M2" t="n">
-        <v>1440581.845941441</v>
-      </c>
       <c r="N2" t="n">
-        <v>1440581.845941441</v>
+        <v>1440581.845941443</v>
       </c>
       <c r="O2" t="n">
         <v>1269155.597801758</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556224.1964558329</v>
+        <v>551386.5909530217</v>
       </c>
       <c r="C4" t="n">
-        <v>554472.2877165735</v>
+        <v>549634.6822137622</v>
       </c>
       <c r="D4" t="n">
-        <v>552718.0024037627</v>
+        <v>547880.3969009516</v>
       </c>
       <c r="E4" t="n">
-        <v>474694.9568742209</v>
+        <v>469906.9358754652</v>
       </c>
       <c r="F4" t="n">
-        <v>498969.5726682167</v>
+        <v>494181.551669461</v>
       </c>
       <c r="G4" t="n">
-        <v>523758.9807925397</v>
+        <v>518970.9597937841</v>
       </c>
       <c r="H4" t="n">
-        <v>522086.0458524425</v>
+        <v>517298.0248536868</v>
       </c>
       <c r="I4" t="n">
-        <v>520410.7754680158</v>
+        <v>515622.7544692601</v>
       </c>
       <c r="J4" t="n">
-        <v>464369.6125335262</v>
+        <v>459704.5839768919</v>
       </c>
       <c r="K4" t="n">
-        <v>462904.8708795845</v>
+        <v>458239.8423229501</v>
       </c>
       <c r="L4" t="n">
-        <v>524533.9144927665</v>
+        <v>519822.4908174392</v>
       </c>
       <c r="M4" t="n">
-        <v>522803.7957912135</v>
+        <v>518092.3721158858</v>
       </c>
       <c r="N4" t="n">
-        <v>521071.1894666612</v>
+        <v>516359.7657913346</v>
       </c>
       <c r="O4" t="n">
-        <v>438916.084163369</v>
+        <v>434251.0556067348</v>
       </c>
       <c r="P4" t="n">
-        <v>398110.3467682332</v>
+        <v>393445.3182115988</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>553073.3017394764</v>
+        <v>557910.9072422881</v>
       </c>
       <c r="C6" t="n">
-        <v>841353.2104787366</v>
+        <v>846190.8159815473</v>
       </c>
       <c r="D6" t="n">
-        <v>843107.4957915465</v>
+        <v>847945.1012943583</v>
       </c>
       <c r="E6" t="n">
-        <v>599982.4200345358</v>
+        <v>604770.4410332913</v>
       </c>
       <c r="F6" t="n">
-        <v>786679.5692884243</v>
+        <v>791467.5902871803</v>
       </c>
       <c r="G6" t="n">
-        <v>813402.8594891297</v>
+        <v>818190.8804878851</v>
       </c>
       <c r="H6" t="n">
-        <v>837475.7944292267</v>
+        <v>842263.8154279826</v>
       </c>
       <c r="I6" t="n">
-        <v>839151.0648136538</v>
+        <v>843939.0858124093</v>
       </c>
       <c r="J6" t="n">
-        <v>369022.7441912306</v>
+        <v>373687.7727478644</v>
       </c>
       <c r="K6" t="n">
-        <v>758583.4858451718</v>
+        <v>763248.514401807</v>
       </c>
       <c r="L6" t="n">
-        <v>769385.4524486754</v>
+        <v>774096.8761240032</v>
       </c>
       <c r="M6" t="n">
-        <v>846315.5711502279</v>
+        <v>851026.9948255557</v>
       </c>
       <c r="N6" t="n">
-        <v>848048.17747478</v>
+        <v>852759.601150108</v>
       </c>
       <c r="O6" t="n">
-        <v>690934.416638389</v>
+        <v>695599.4451950237</v>
       </c>
       <c r="P6" t="n">
-        <v>722957.0896586057</v>
+        <v>727622.1182152402</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27005,10 +27005,10 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27436,10 +27436,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>307.3903671255648</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
@@ -27448,7 +27448,7 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
@@ -27484,10 +27484,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>307.3903671255646</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27521,10 +27521,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>41.70910106771527</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27533,7 +27533,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27563,13 +27563,13 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>342.2743756165772</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>326.5849064336912</v>
       </c>
       <c r="C4" t="n">
         <v>272.7252466480447</v>
@@ -27603,13 +27603,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
@@ -27645,22 +27645,22 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>232.998691691247</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27679,7 +27679,7 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>307.3903671255646</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27736,10 +27736,10 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>307.3903671255647</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -27752,16 +27752,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>185.682627621886</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>115.3536407070568</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27831,25 +27831,25 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>384.1281642552197</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>322.6095995970861</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27916,7 +27916,7 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27958,10 +27958,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>56.51176829727007</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27970,13 +27970,13 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
+        <v>56.51176829727058</v>
+      </c>
+      <c r="X8" t="n">
         <v>400</v>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -27992,16 +27992,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>210.6860087135172</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>172.5204020740694</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,13 +28065,13 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C10" t="n">
+        <v>384.1281642552244</v>
+      </c>
+      <c r="D10" t="n">
         <v>400</v>
-      </c>
-      <c r="C10" t="n">
-        <v>272.7252466480447</v>
-      </c>
-      <c r="D10" t="n">
-        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
@@ -28080,16 +28080,16 @@
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>355.194425911052</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28116,16 +28116,16 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
@@ -28247,7 +28247,7 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>19.11687125883891</v>
+        <v>225</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>225</v>
+        <v>19.11687125883863</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28484,22 +28484,22 @@
         <v>251</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>166.1982915220773</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>251</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
-        <v>166.1982915220775</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>251</v>
@@ -28721,10 +28721,10 @@
         <v>279</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -28736,10 +28736,10 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>155.6705902671032</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>279</v>
@@ -28958,22 +28958,22 @@
         <v>279</v>
       </c>
       <c r="J21" t="n">
+        <v>155.6705902671031</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>279</v>
-      </c>
-      <c r="K21" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -29195,16 +29195,16 @@
         <v>279</v>
       </c>
       <c r="J24" t="n">
+        <v>279</v>
+      </c>
+      <c r="K24" t="n">
         <v>155.6705902671031</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -29429,7 +29429,7 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J27" t="n">
         <v>225</v>
@@ -29444,10 +29444,10 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>26.99048536749072</v>
+        <v>225</v>
       </c>
       <c r="O27" t="n">
-        <v>225</v>
+        <v>19.11687125883898</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
@@ -29669,7 +29669,7 @@
         <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>225</v>
+        <v>19.11687125883917</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29687,7 +29687,7 @@
         <v>225</v>
       </c>
       <c r="P30" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q30" t="n">
         <v>225</v>
@@ -29806,7 +29806,7 @@
         <v>291</v>
       </c>
       <c r="C32" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="D32" t="n">
         <v>291</v>
@@ -29821,7 +29821,7 @@
         <v>291</v>
       </c>
       <c r="H32" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="I32" t="n">
         <v>150.0811596826846</v>
@@ -29903,10 +29903,10 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
-        <v>227.0158611578289</v>
+        <v>291</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>227.015861157829</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -29924,7 +29924,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>291</v>
@@ -29964,7 +29964,7 @@
         <v>291</v>
       </c>
       <c r="C34" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="D34" t="n">
         <v>291</v>
@@ -29973,7 +29973,7 @@
         <v>291</v>
       </c>
       <c r="F34" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="G34" t="n">
         <v>291</v>
@@ -30030,7 +30030,7 @@
         <v>291</v>
       </c>
       <c r="Y34" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35">
@@ -30058,10 +30058,10 @@
         <v>291</v>
       </c>
       <c r="H35" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="I35" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30149,7 +30149,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>227.0158611578289</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -30161,7 +30161,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>227.0158611578287</v>
       </c>
       <c r="Q36" t="n">
         <v>291</v>
@@ -30298,7 +30298,7 @@
         <v>291</v>
       </c>
       <c r="I38" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30380,7 +30380,7 @@
         <v>291</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>227.015861157829</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30398,7 +30398,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>227.0158611578287</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>291</v>
@@ -30438,7 +30438,7 @@
         <v>291</v>
       </c>
       <c r="C40" t="n">
-        <v>291</v>
+        <v>291.0000000000276</v>
       </c>
       <c r="D40" t="n">
         <v>291</v>
@@ -30447,7 +30447,7 @@
         <v>291</v>
       </c>
       <c r="F40" t="n">
-        <v>291</v>
+        <v>291.0000000000276</v>
       </c>
       <c r="G40" t="n">
         <v>291</v>
@@ -30620,7 +30620,7 @@
         <v>213</v>
       </c>
       <c r="K42" t="n">
-        <v>213</v>
+        <v>158.5978143635403</v>
       </c>
       <c r="L42" t="n">
         <v>213</v>
@@ -30635,7 +30635,7 @@
         <v>213</v>
       </c>
       <c r="P42" t="n">
-        <v>158.5978143635402</v>
+        <v>213</v>
       </c>
       <c r="Q42" t="n">
         <v>213</v>
@@ -30696,7 +30696,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>65.00462472645802</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30729,7 +30729,7 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9583912744579</v>
+        <v>180.6940671650082</v>
       </c>
       <c r="V43" t="n">
         <v>199.1703102162162</v>
@@ -30854,7 +30854,7 @@
         <v>187</v>
       </c>
       <c r="J45" t="n">
-        <v>187</v>
+        <v>79.79463078200436</v>
       </c>
       <c r="K45" t="n">
         <v>187</v>
@@ -30872,7 +30872,7 @@
         <v>187</v>
       </c>
       <c r="P45" t="n">
-        <v>39.96025170009777</v>
+        <v>187</v>
       </c>
       <c r="Q45" t="n">
         <v>173.0792650904796</v>
@@ -30933,7 +30933,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>105.510885102291</v>
+        <v>71.17842411646478</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>187</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34746,10 +34746,10 @@
         <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L2" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M2" t="n">
         <v>814</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>39.47110609661257</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -34889,13 +34889,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>223.3665443798817</v>
@@ -34931,22 +34931,22 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>33.8283814750308</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,7 +34983,7 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -35117,25 +35117,25 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>111.402917607175</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>364.7310511640923</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>75.16595416697857</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35235,7 +35235,7 @@
         <v>814</v>
       </c>
       <c r="P8" t="n">
-        <v>814</v>
+        <v>814.0000000000045</v>
       </c>
       <c r="Q8" t="n">
         <v>814</v>
@@ -35351,13 +35351,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>111.4029176071796</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
@@ -35366,16 +35366,16 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>126.4232998094333</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35402,16 +35402,16 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P11" t="n">
-        <v>629.7921402269702</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>161.5508809199775</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35533,7 +35533,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>144.3254774965146</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734918</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35697,7 +35697,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,10 +35706,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>814</v>
+        <v>435.3966095009885</v>
       </c>
       <c r="P14" t="n">
-        <v>435.3966095009885</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35770,22 +35770,22 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>291.406897759753</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>525.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>86.95004216450428</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>300.8248416307323</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>364.6660045146532</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>161.5508809199775</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,10 +36007,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>346.7744449078945</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
@@ -36022,10 +36022,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>397.1276121698496</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
         <v>105.9207349095204</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>161.5508809199773</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,10 +36244,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>404.2086062376757</v>
+        <v>280.8791965047788</v>
       </c>
       <c r="K21" t="n">
-        <v>346.7744449078945</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36259,7 +36259,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P21" t="n">
         <v>113.6660045146532</v>
@@ -36414,10 +36414,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>240.8110739199409</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>814</v>
+        <v>435.3966095009883</v>
       </c>
       <c r="P23" t="n">
         <v>814</v>
@@ -36481,16 +36481,16 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>280.8791965047788</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>191.1038546407913</v>
+        <v>346.7744449078945</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
         <v>134.6265501086548</v>
@@ -36642,7 +36642,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36654,10 +36654,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>314.0531751575265</v>
       </c>
       <c r="P26" t="n">
-        <v>370.1780576344547</v>
+        <v>773.0000000000275</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
         <v>350.2086062376757</v>
@@ -36730,10 +36730,10 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>161.6170354761456</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
@@ -36879,10 +36879,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,13 +36891,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>314.0531751575191</v>
       </c>
       <c r="P29" t="n">
-        <v>40.20744657654306</v>
+        <v>773.0000000000348</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36955,7 +36955,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -36973,7 +36973,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
         <v>51.92073490952041</v>
@@ -37116,10 +37116,10 @@
         <v>773.0000000000421</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320763738</v>
+        <v>727.1079320765427</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>773.0000000000421</v>
@@ -37189,10 +37189,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>9.889475266480316</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>352.2244673955047</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
@@ -37210,7 +37210,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>404.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>117.9207349095204</v>
@@ -37250,7 +37250,7 @@
         <v>3.886199662921342</v>
       </c>
       <c r="C34" t="n">
-        <v>18.27475335195533</v>
+        <v>18.27475335197925</v>
       </c>
       <c r="D34" t="n">
         <v>5.46378194444452</v>
@@ -37259,7 +37259,7 @@
         <v>10.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>16.61714403225807</v>
+        <v>16.61714403228201</v>
       </c>
       <c r="G34" t="n">
         <v>45.95612715846997</v>
@@ -37316,7 +37316,7 @@
         <v>43.55635456989245</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.534647150561582</v>
+        <v>3.534647150537637</v>
       </c>
     </row>
     <row r="35">
@@ -37353,10 +37353,10 @@
         <v>773.0000000000493</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760313</v>
+        <v>773</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>727.1079320760799</v>
       </c>
       <c r="M35" t="n">
         <v>773.0000000000493</v>
@@ -37435,7 +37435,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>501.1072365065158</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
         <v>86.95004216450428</v>
@@ -37447,7 +37447,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>113.6660045146532</v>
+        <v>340.6818656724819</v>
       </c>
       <c r="Q36" t="n">
         <v>117.9207349095204</v>
@@ -37590,7 +37590,7 @@
         <v>773.0000000000566</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320759773</v>
+        <v>727.1079320765475</v>
       </c>
       <c r="L38" t="n">
         <v>773</v>
@@ -37666,7 +37666,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>125.2086062376757</v>
+        <v>352.2244673955047</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37684,7 +37684,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>340.6818656724819</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
         <v>117.9207349095204</v>
@@ -37724,7 +37724,7 @@
         <v>3.886199662921342</v>
       </c>
       <c r="C40" t="n">
-        <v>18.27475335195533</v>
+        <v>18.27475335198289</v>
       </c>
       <c r="D40" t="n">
         <v>5.46378194444452</v>
@@ -37733,7 +37733,7 @@
         <v>10.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>16.61714403225807</v>
+        <v>16.61714403228565</v>
       </c>
       <c r="G40" t="n">
         <v>45.95612715846997</v>
@@ -37824,25 +37824,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>160.4676395763792</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>773.0000000000639</v>
+        <v>765.439787975521</v>
       </c>
       <c r="P41" t="n">
-        <v>773.0000000000639</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37906,7 +37906,7 @@
         <v>338.2086062376757</v>
       </c>
       <c r="K42" t="n">
-        <v>404.1038546407913</v>
+        <v>349.7016690043316</v>
       </c>
       <c r="L42" t="n">
         <v>487.091375348687</v>
@@ -37921,7 +37921,7 @@
         <v>454.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>272.2638188781934</v>
+        <v>326.6660045146532</v>
       </c>
       <c r="Q42" t="n">
         <v>39.92073490952041</v>
@@ -37982,40 +37982,40 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
         <v>29.73567589055027</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>314.0531751574757</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38076,7 +38076,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>773.0000000000784</v>
+        <v>765.439787975521</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>312.2086062376757</v>
+        <v>205.0032370196801</v>
       </c>
       <c r="K45" t="n">
         <v>378.1038546407913</v>
@@ -38158,7 +38158,7 @@
         <v>428.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>153.626256214751</v>
+        <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>70.24193626638326</v>
+        <v>35.909475280557</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>36.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
